--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -553,13 +553,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="3">
-        <f>HYPERLINK("https://wa.me/96524831136?text=Hello%20Akrram%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Akrram%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/akrram/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96524831136")</f>
-        <v/>
-      </c>
-      <c r="F2" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","View Demo Site")</f>
-        <v/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+96524831136  (wa.me/96524831136)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+        </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -595,13 +597,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Aqua%20Terre%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Aqua%20Terre%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F3" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","View Demo Site")</f>
-        <v/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+        </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -637,13 +641,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Bio%20Sphere%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F4" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -679,13 +685,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Carribean%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Carribean%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+        </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -721,13 +729,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Gulf%20Salon%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Gulf%20Salon%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F6" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+        </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -763,13 +773,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Herbal%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Herbal%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F7" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+        </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -805,13 +817,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lalique%20Beauty%20Centre%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Lalique%20Beauty%20Centre%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","View Demo Site")</f>
-        <v/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+        </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -847,13 +861,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F9" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+        </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -889,13 +905,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Nail%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Nail%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/nail-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F10" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+        </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -931,13 +949,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Pana%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Pana%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/pana-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F11" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+        </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -973,13 +993,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Reem%20Palace%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Reem%20Palace%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/reem-palace/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F12" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","View Demo Site")</f>
-        <v/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1015,13 +1037,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Saledaire%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Saledaire%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/saledaire/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","View Demo Site")</f>
-        <v/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1057,13 +1081,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20The%20Body%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F14" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1099,13 +1125,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Lounge%20Spa%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20The%20Lounge%20Spa%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F15" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+        </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1141,13 +1169,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Virgin%20Touch%20Salon%21%20This%20is%20Faizan%20from%20KB%20Rewaq%20Digital%20%E2%80%94%20Kuwait.%0AWe%20build%20websites%20%2B%20run%20Instagram/social%20%2B%20paid%20ads%20for%20ladies%20salons%20%26%20spas.%0AI%20made%20a%20free%20demo%20site%20for%20Virgin%20Touch%20Salon%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/%0AOur%20packages%20start%20at%20just%2035%20KWD/month%20%28Tier%201%29.%2050%25%20advance%2C%203-day%20delivery%2C%20cash/bank%20ok.%0AMay%20I%20share%20the%20full%20packages%3F%20No%20pressure%20at%20all.","+96550703252")</f>
-        <v/>
-      </c>
-      <c r="F16" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  (wa.me/96550703252)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+        </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -553,23 +553,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>+96524831136  (wa.me/96524831136)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
-        </is>
+      <c r="E2" s="3">
+        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F2" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Hello Akrram! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Akrram: https://faizanbashar215.github.io/kb-rewaq-digital/akrram/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -597,23 +591,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
-        </is>
+      <c r="E3" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F3" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Hello Aqua Terre! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Aqua Terre: https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -641,23 +629,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
-        </is>
+      <c r="E4" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Hello Bio Sphere Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Bio Sphere Spa: https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -685,23 +667,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
-        </is>
+      <c r="E5" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Hello Carribean Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Carribean Spa: https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -729,23 +705,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
-        </is>
+      <c r="E6" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hello Gulf Salon! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Gulf Salon: https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -773,23 +743,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
-        </is>
+      <c r="E7" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F7" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hello Herbal Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Herbal Spa: https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -817,23 +781,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
-        </is>
+      <c r="E8" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Hello Lalique Beauty Centre! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Lalique Beauty Centre: https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -861,23 +819,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
-        </is>
+      <c r="E9" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F9" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Hello Lamsat Al Badoor Ladies' Salon! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Lamsat Al Badoor Ladies' Salon: https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -905,23 +857,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
-        </is>
+      <c r="E10" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F10" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Hello Nail Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Nail Spa: https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -949,23 +895,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
-        </is>
+      <c r="E11" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F11" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Hello Pana Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Pana Spa: https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -993,23 +933,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
-        </is>
+      <c r="E12" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F12" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Hello Reem Palace! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Reem Palace: https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1037,23 +971,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
-        </is>
+      <c r="E13" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F13" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Hello Saledaire! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Saledaire: https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1081,23 +1009,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
-        </is>
+      <c r="E14" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F14" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Hello The Body Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for The Body Spa: https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1125,23 +1047,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
-        </is>
+      <c r="E15" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F15" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Hello The Lounge Spa! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for The Lounge Spa: https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1169,23 +1085,17 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>+96550703252  (wa.me/96550703252)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
-        </is>
+      <c r="E16" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","View Demo Site")</f>
+        <v/>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Hello Virgin Touch Salon! This is Faizan from KB Rewaq Digital — Kuwait.
-We build websites + run Instagram/social + paid ads for ladies salons &amp; spas.
-I made a free demo site for Virgin Touch Salon: https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/
-Our packages start at just 35 KWD/month (Tier 1). 50% advance, 3-day delivery, cash/bank ok.
-May I share the full packages? No pressure at all.</t>
+          <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -553,13 +553,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="3">
-        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F2" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","View Demo Site")</f>
-        <v/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+96524831136  |  wa.me/96524831136</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+        </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -591,13 +593,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F3" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","View Demo Site")</f>
-        <v/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+        </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -629,13 +633,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F4" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -667,13 +673,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+        </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -705,13 +713,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F6" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+        </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -743,13 +753,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F7" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+        </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -781,13 +793,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F8" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","View Demo Site")</f>
-        <v/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+        </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -819,13 +833,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F9" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+        </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -857,13 +873,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F10" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+        </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -895,13 +913,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F11" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+        </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -933,13 +953,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F12" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","View Demo Site")</f>
-        <v/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -971,13 +993,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","View Demo Site")</f>
-        <v/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1009,13 +1033,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F14" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1047,13 +1073,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F15" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","View Demo Site")</f>
-        <v/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+        </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1085,13 +1113,15 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F16" s="4">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","View Demo Site")</f>
-        <v/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+96550703252  |  wa.me/96550703252</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+        </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="00006100"/>
     </font>
     <font>
       <color rgb="000563C1"/>
@@ -47,17 +44,12 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -96,9 +88,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,13 +99,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,17 +468,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,20 +506,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phone (click→WhatsApp)</t>
+          <t>Phone (copy)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Demo Website (click)</t>
+          <t>Click to DM (WhatsApp)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Ready DM Message (link inside)</t>
+          <t>Demo Website (copy URL)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Demo (click)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ready DM Message</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,22 +554,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>+96524831136  |  wa.me/96524831136</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3">
+        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -593,22 +602,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -633,22 +650,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -673,22 +698,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -713,22 +746,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -753,22 +794,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -793,22 +842,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -833,22 +890,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -873,22 +938,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -913,22 +986,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -953,22 +1034,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -993,22 +1082,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1033,22 +1130,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1073,22 +1178,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1113,22 +1226,30 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>+96550703252  |  wa.me/96550703252</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="3">
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","Open Site")</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1145,14 +1266,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>KB REWAQ DIGITAL — FRESH LEAD TRACKER</t>
         </is>
@@ -1164,45 +1285,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Click the GREEN phone cell -&gt; opens WhatsApp to that lead with your DM pre-typed.</t>
+          <t>1. Column E (Phone copy) = plain number + wa.me link. Copy-paste or open wa.me manually.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Click the BLUE 'View Demo Site' cell -&gt; opens the website built for them.</t>
+          <t>2. Column F (Click to DM) = BLUE link. Open this Excel file in Excel/Google Sheets and CLICK it -&gt; WhatsApp opens with the DM already typed. One click sends.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Send the DM on WhatsApp. The link is already inside the message.</t>
+          <t>3. Column G (Demo URL) = plain website link to copy.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. When they reply YES, visit their salon, then discuss price &amp; sign up.</t>
+          <t>4. Column H (Demo click) = BLUE link. Click to open their demo site.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. After sending, change Status to: replied / won / paid.</t>
+          <t>5. Column I = full DM text (human, English, Jarvis intro, no price).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6. Send DM via Column F. When they reply YES, visit salon, discuss price, sign up.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Your WA: +96550703252   |   Brand: KB Rewaq Digital</t>
+          <t>7. Change Status (col J) to: replied / won / paid.</t>
         </is>
       </c>
     </row>
@@ -1211,6 +1336,16 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>Your WA: +96550703252   |   Brand: KB Rewaq Digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Total fresh leads: 15   |   Live demo sites: 15</t>
         </is>

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -468,19 +468,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -506,30 +504,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phone (copy)</t>
+          <t>Click to DM (WhatsApp)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Click to DM (WhatsApp)</t>
+          <t>View Demo Website</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Demo Website (copy URL)</t>
+          <t>Ready DM Message</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Demo (click)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Ready DM Message</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -554,30 +542,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>+96524831136  |  wa.me/96524831136</t>
-        </is>
+      <c r="E2" s="3">
+        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/akrram/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F2" s="3">
-        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","View Demo")</f>
         <v/>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
-        </is>
-      </c>
-      <c r="H2" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
+          <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -602,30 +581,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E3" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F3" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","View Demo")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
-        </is>
-      </c>
-      <c r="H3" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+          <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -650,30 +620,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E4" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F4" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
-        </is>
-      </c>
-      <c r="H4" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+          <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -698,30 +659,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E5" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F5" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
-        </is>
-      </c>
-      <c r="H5" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
+          <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -746,30 +698,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E6" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F6" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
-        </is>
-      </c>
-      <c r="H6" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+          <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -794,30 +737,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E7" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F7" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
-        </is>
-      </c>
-      <c r="H7" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+          <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -842,30 +776,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E8" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F8" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","View Demo")</f>
         <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
-        </is>
-      </c>
-      <c r="H8" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+          <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -890,30 +815,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E9" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F9" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
-        </is>
-      </c>
-      <c r="H9" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+          <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -938,30 +854,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E10" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F10" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
-        </is>
-      </c>
-      <c r="H10" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+          <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -986,30 +893,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E11" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F11" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
-        </is>
-      </c>
-      <c r="H11" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+          <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1034,30 +932,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E12" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F12" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","View Demo")</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
-        </is>
-      </c>
-      <c r="H12" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+          <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1082,30 +971,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E13" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/saledaire/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F13" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","View Demo")</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
-        </is>
-      </c>
-      <c r="H13" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+          <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1130,30 +1010,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E14" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F14" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
-        </is>
-      </c>
-      <c r="H14" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+          <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1178,30 +1049,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E15" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F15" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
-        </is>
-      </c>
-      <c r="H15" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+          <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1226,30 +1088,21 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  wa.me/96550703252</t>
-        </is>
+      <c r="E16" s="3">
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","Click to DM")</f>
+        <v/>
       </c>
       <c r="F16" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.","Click to DM")</f>
+        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
-        </is>
-      </c>
-      <c r="H16" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","Open Site")</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+          <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -475,7 +475,7 @@
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Phone &amp; Website</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Click to DM (WhatsApp)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>View Demo Website</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -542,12 +542,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>+96524831136  |  https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+        </is>
+      </c>
+      <c r="F2" s="3">
         <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/akrram/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F2" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/akrram/","View Demo")</f>
         <v/>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -581,12 +582,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+        </is>
+      </c>
+      <c r="F3" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F3" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","View Demo")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -620,12 +622,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+        </is>
+      </c>
+      <c r="F4" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F4" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -659,12 +662,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+        </is>
+      </c>
+      <c r="F5" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F5" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -698,12 +702,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+        </is>
+      </c>
+      <c r="F6" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F6" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -737,12 +742,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+        </is>
+      </c>
+      <c r="F7" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F7" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -776,12 +782,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+        </is>
+      </c>
+      <c r="F8" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F8" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","View Demo")</f>
         <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -815,12 +822,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+        </is>
+      </c>
+      <c r="F9" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F9" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -854,12 +862,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+        </is>
+      </c>
+      <c r="F10" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F10" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -893,12 +902,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+        </is>
+      </c>
+      <c r="F11" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F11" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -932,12 +942,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+        </is>
+      </c>
+      <c r="F12" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F12" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","View Demo")</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -971,12 +982,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+        </is>
+      </c>
+      <c r="F13" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/saledaire/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F13" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/","View Demo")</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1010,12 +1022,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+        </is>
+      </c>
+      <c r="F14" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F14" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1049,12 +1062,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+        </is>
+      </c>
+      <c r="F15" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F15" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","View Demo")</f>
         <v/>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1088,12 +1102,13 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+        </is>
+      </c>
+      <c r="F16" s="3">
         <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="F16" s="3">
-        <f>HYPERLINK("https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","View Demo")</f>
         <v/>
       </c>
       <c r="G16" s="2" t="inlineStr">

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -544,17 +544,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>+96524831136  |  https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+          <t>+96524831136  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/</t>
         </is>
       </c>
       <c r="F2" s="3">
-        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/akrram/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/","Click to DM")</f>
         <v/>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/akrram/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
         </is>
       </c>
       <c r="F3" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/","Click to DM")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/aqua-terre/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+          <t>+96529833784  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/</t>
         </is>
       </c>
       <c r="F4" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96529833784?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/bio-sphere-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -664,17 +664,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+          <t>+96521208484  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/</t>
         </is>
       </c>
       <c r="F5" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96521208484?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/carribean-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
         </is>
       </c>
       <c r="F6" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/gulf-salon/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
         </is>
       </c>
       <c r="F7" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/herbal-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
         </is>
       </c>
       <c r="F8" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/","Click to DM")</f>
         <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/lalique-beauty-centre/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+          <t>+96556138028  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/</t>
         </is>
       </c>
       <c r="F9" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96556138028?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/lamsat-al-badoor-ladies-salon/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
         </is>
       </c>
       <c r="F10" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/nail-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/nail-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
         </is>
       </c>
       <c r="F11" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/pana-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/pana-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+          <t>+96521796465  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/</t>
         </is>
       </c>
       <c r="F12" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/reem-palace/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96521796465?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/","Click to DM")</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/reem-palace/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
         </is>
       </c>
       <c r="F13" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/saledaire/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/","Click to DM")</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/saledaire/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
         </is>
       </c>
       <c r="F14" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/the-body-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+          <t>+96520230711  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/</t>
         </is>
       </c>
       <c r="F15" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96520230711?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/the-lounge-spa/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/</t>
         </is>
       </c>
       <c r="F16" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/virgin-touch-salon/</t>
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -584,11 +584,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
+          <t>+96593633099  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
         </is>
       </c>
       <c r="F3" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96593633099?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/","Click to DM")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -704,11 +704,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
+          <t>+96599283511  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
         </is>
       </c>
       <c r="F6" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96599283511?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
+          <t>+96528773667  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
         </is>
       </c>
       <c r="F7" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96528773667?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -784,11 +784,11 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
+          <t>+96574620131  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
         </is>
       </c>
       <c r="F8" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96574620131?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/","Click to DM")</f>
         <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -864,11 +864,11 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
+          <t>+96522658869  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
         </is>
       </c>
       <c r="F10" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96522658869?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
+          <t>+96522468343  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
         </is>
       </c>
       <c r="F11" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96522468343?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -984,11 +984,11 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
+          <t>+96523982936  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
         </is>
       </c>
       <c r="F13" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96523982936?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/","Click to DM")</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
+          <t>+96527871478  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
         </is>
       </c>
       <c r="F14" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96527871478?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/","Click to DM")</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">

--- a/KB_Rewaq_Fresh_Leads.xlsx
+++ b/KB_Rewaq_Fresh_Leads.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -529,32 +529,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Akrram</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>صالون Akrram</t>
-        </is>
-      </c>
+          <t>Beautytek for Women</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>+96524831136  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/</t>
+          <t>+96566717137  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/beautytek-for-women/</t>
         </is>
       </c>
       <c r="F2" s="3">
-        <f>HYPERLINK("https://wa.me/96524831136?text=Hey%20Akrram.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Akrram%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96566717137?text=Hey%20Beautytek%20for%20Women.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Salmiya.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Beautytek%20for%20Women%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/beautytek-for-women/","Click to DM")</f>
         <v/>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Hey Akrram. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Akrram caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/akrram/</t>
+          <t>Hey Beautytek for Women. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Salmiya. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Beautytek for Women caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/beautytek-for-women/</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -569,32 +565,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Aqua Terre</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>صالون Aqua Terre</t>
-        </is>
-      </c>
+          <t>Dar Wed Beauty Salon</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Fintas</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>+96593633099  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
+          <t>+96550906693  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dar-wed-beauty-salon/</t>
         </is>
       </c>
       <c r="F3" s="3">
-        <f>HYPERLINK("https://wa.me/96593633099?text=Hi%20Aqua%20Terre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Aqua%20Terre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96550906693?text=Hi%20Dar%20Wed%20Beauty%20Salon.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Fintas.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Dar%20Wed%20Beauty%20Salon%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dar-wed-beauty-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Hi Aqua Terre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Aqua Terre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/aqua-terre/</t>
+          <t>Hi Dar Wed Beauty Salon. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Fintas. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Dar Wed Beauty Salon and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dar-wed-beauty-salon/</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -609,32 +601,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Bio Sphere Spa</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>صالون Bio Sphere Spa</t>
-        </is>
-      </c>
+          <t>Dodo Beauty Salon</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Khaitan</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>+96529833784  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/</t>
+          <t>+96569654343  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dodo-beauty-salon/</t>
         </is>
       </c>
       <c r="F4" s="3">
-        <f>HYPERLINK("https://wa.me/96529833784?text=Hello%20Bio%20Sphere%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Bio%20Sphere%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96569654343?text=Hello%20Dodo%20Beauty%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Khaitan.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Dodo%20Beauty%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dodo-beauty-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Hello Bio Sphere Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Bio Sphere Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/bio-sphere-spa/</t>
+          <t>Hello Dodo Beauty Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Khaitan. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Dodo Beauty Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/dodo-beauty-salon/</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -649,32 +637,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Carribean Spa</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>صالون Carribean Spa</t>
-        </is>
-      </c>
+          <t>Edit Salon</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Rigga (Al-Riqae)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>+96521208484  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/</t>
+          <t>+96597726616  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/edit-salon/</t>
         </is>
       </c>
       <c r="F5" s="3">
-        <f>HYPERLINK("https://wa.me/96521208484?text=Good%20day%20Carribean%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Carribean%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96597726616?text=Good%20day%20Edit%20Salon.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Rigga%20%28Al-Riqae%29.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Edit%20Salon%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/edit-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Good day Carribean Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Carribean Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/carribean-spa/</t>
+          <t>Good day Edit Salon. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Rigga (Al-Riqae). Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Edit Salon and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/edit-salon/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -689,32 +673,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Gulf Salon</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>صالون Gulf Salon</t>
-        </is>
-      </c>
+          <t>Fadwa Beauty Home Service</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+96599283511  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
+          <t>+96594408664  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/fadwa-beauty-home-service/</t>
         </is>
       </c>
       <c r="F6" s="3">
-        <f>HYPERLINK("https://wa.me/96599283511?text=Hi%20there%20Gulf%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Gulf%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96594408664?text=Hi%20there%20Fadwa%20Beauty%20Home%20Service.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Salmiya.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Fadwa%20Beauty%20Home%20Service%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/fadwa-beauty-home-service/","Click to DM")</f>
         <v/>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Hi there Gulf Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Gulf Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/gulf-salon/</t>
+          <t>Hi there Fadwa Beauty Home Service. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Salmiya. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Fadwa Beauty Home Service and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/fadwa-beauty-home-service/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -729,32 +709,28 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Herbal Spa</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>صالون Herbal Spa</t>
-        </is>
-      </c>
+          <t>Hair Lounge Kuwait</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>+96528773667  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
+          <t>+96541165200  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/hair-lounge-kuwait/</t>
         </is>
       </c>
       <c r="F7" s="3">
-        <f>HYPERLINK("https://wa.me/96528773667?text=Hey%20Herbal%20Spa.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Herbal%20Spa%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96541165200?text=Hey%20Hair%20Lounge%20Kuwait.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Salmiya.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Hair%20Lounge%20Kuwait%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/hair-lounge-kuwait/","Click to DM")</f>
         <v/>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Hey Herbal Spa. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Herbal Spa caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/herbal-spa/</t>
+          <t>Hey Hair Lounge Kuwait. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Salmiya. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Hair Lounge Kuwait caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/hair-lounge-kuwait/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -769,32 +745,28 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lalique Beauty Centre</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>صالون Lalique Beauty Centre</t>
-        </is>
-      </c>
+          <t>Kabayan Kuwait 24/7 Beauty</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Kuwait City (Sharq)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>+96574620131  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
+          <t>+96597963565  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/kabayan-kuwait-24-7-beauty/</t>
         </is>
       </c>
       <c r="F8" s="3">
-        <f>HYPERLINK("https://wa.me/96574620131?text=Hi%20Lalique%20Beauty%20Centre.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Lalique%20Beauty%20Centre%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96597963565?text=Hi%20Kabayan%20Kuwait%2024/7%20Beauty.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait%20City%20%28Sharq%29.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Kabayan%20Kuwait%2024/7%20Beauty%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/kabayan-kuwait-24-7-beauty/","Click to DM")</f>
         <v/>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Hi Lalique Beauty Centre. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Lalique Beauty Centre and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lalique-beauty-centre/</t>
+          <t>Hi Kabayan Kuwait 24/7 Beauty. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait City (Sharq). The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Kabayan Kuwait 24/7 Beauty and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/kabayan-kuwait-24-7-beauty/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -809,32 +781,28 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Lamsat Al Badoor Ladies' Salon</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>صالون Lamsat Al Badoor Ladies' Salon</t>
-        </is>
-      </c>
+          <t>Lulu Khaitan salon shop 3&amp;4</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Khaitan</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>+96556138028  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/</t>
+          <t>+96597280415  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lulu-khaitan-salon-shop-3-4/</t>
         </is>
       </c>
       <c r="F9" s="3">
-        <f>HYPERLINK("https://wa.me/96556138028?text=Hello%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lamsat%20Al%20Badoor%20Ladies%27%20Salon%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96597280415?text=Hello%20Lulu%20Khaitan%20salon%20shop%203%264.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Khaitan.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20Lulu%20Khaitan%20salon%20shop%203%264%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lulu-khaitan-salon-shop-3-4/","Click to DM")</f>
         <v/>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Hello Lamsat Al Badoor Ladies' Salon. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lamsat Al Badoor Ladies' Salon stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lamsat-al-badoor-ladies-salon/</t>
+          <t>Hello Lulu Khaitan salon shop 3&amp;4. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Khaitan. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. Lulu Khaitan salon shop 3&amp;4 stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/lulu-khaitan-salon-shop-3-4/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -849,32 +817,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nail Spa</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>صالون Nail Spa</t>
-        </is>
-      </c>
+          <t>Monya.Salon</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>+96522658869  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
+          <t>+96598980970  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/monya-salon/</t>
         </is>
       </c>
       <c r="F10" s="3">
-        <f>HYPERLINK("https://wa.me/96522658869?text=Good%20day%20Nail%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Nail%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96598980970?text=Good%20day%20Monya.Salon.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Salmiya.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Monya.Salon%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/monya-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Good day Nail Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Nail Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/nail-spa/</t>
+          <t>Good day Monya.Salon. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Salmiya. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Monya.Salon and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/monya-salon/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -889,32 +853,28 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Pana Spa</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>صالون Pana Spa</t>
-        </is>
-      </c>
+          <t>Qalusi Salon</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Mangaf</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>+96522468343  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
+          <t>+96557556872  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/qalusi-salon/</t>
         </is>
       </c>
       <c r="F11" s="3">
-        <f>HYPERLINK("https://wa.me/96522468343?text=Hi%20there%20Pana%20Spa.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Pana%20Spa%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96557556872?text=Hi%20there%20Qalusi%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Mangaf.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Qalusi%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/qalusi-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Hi there Pana Spa. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Pana Spa and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/pana-spa/</t>
+          <t>Hi there Qalusi Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Mangaf. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Qalusi Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/qalusi-salon/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -929,32 +889,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Reem Palace</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>صالون Reem Palace</t>
-        </is>
-      </c>
+          <t>The Bay Salon</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>+96521796465  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/</t>
+          <t>+96598875922  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-bay-salon/</t>
         </is>
       </c>
       <c r="F12" s="3">
-        <f>HYPERLINK("https://wa.me/96521796465?text=Hey%20Reem%20Palace.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Kuwait.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20Reem%20Palace%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96598875922?text=Hey%20The%20Bay%20Salon.%20This%20is%20Jarvis%20from%20KB%20Rewaq%20Digital.%20I%20run%20automation%20for%20Kuwait%20beauty%20businesses.%20Based%20in%20Salmiya.%20You%20get%20a%20website%2C%20fresh%20Instagram%20content%2C%20and%20an%20auto-reply%20WhatsApp%20that%20takes%20bookings%20even%20when%20you%20are%20busy%20with%20clients.%20Your%20salon%20The%20Bay%20Salon%20caught%20my%20eye%20and%20this%20system%20would%20suit%20you.%20I%20can%20show%20you%20a%20free%20demo%20of%20your%20own%20site%20within%20a%20day.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-bay-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Hey Reem Palace. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Kuwait. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon Reem Palace caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/reem-palace/</t>
+          <t>Hey The Bay Salon. This is Jarvis from KB Rewaq Digital. I run automation for Kuwait beauty businesses. Based in Salmiya. You get a website, fresh Instagram content, and an auto-reply WhatsApp that takes bookings even when you are busy with clients. Your salon The Bay Salon caught my eye and this system would suit you. I can show you a free demo of your own site within a day.
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-bay-salon/</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -969,32 +925,28 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Saledaire</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>صالون Saledaire</t>
-        </is>
-      </c>
+          <t>The French Beauty Kuwait (Mangaf br.)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Mangaf</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>+96523982936  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
+          <t>+96566468458  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-mangaf-br/</t>
         </is>
       </c>
       <c r="F13" s="3">
-        <f>HYPERLINK("https://wa.me/96523982936?text=Hi%20Saledaire.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Kuwait.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20Saledaire%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96566468458?text=Hi%20The%20French%20Beauty%20Kuwait%20%28Mangaf%20br.%29.%20Jarvis%20here%2C%20I%20manage%20KB%20Rewaq%20Digital%20where%20we%20automate%20Kuwait%20salons%20end%20to%20end.%20Based%20in%20Mangaf.%20The%20setup%20is%20a%20website%20plus%20Instagram%20plus%20a%20WhatsApp%20assistant%20that%20handles%20client%20bookings%20on%20its%20own.%20I%20noticed%20The%20French%20Beauty%20Kuwait%20%28Mangaf%20br.%29%20and%20believe%20this%20would%20work%20great%20for%20you.%20A%20free%20demo%20of%20your%20site%20takes%20me%20about%20a%20day%20to%20make.%20Shall%20I%20send%20it%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-mangaf-br/","Click to DM")</f>
         <v/>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Hi Saledaire. Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Kuwait. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed Saledaire and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/saledaire/</t>
+          <t>Hi The French Beauty Kuwait (Mangaf br.). Jarvis here, I manage KB Rewaq Digital where we automate Kuwait salons end to end. Based in Mangaf. The setup is a website plus Instagram plus a WhatsApp assistant that handles client bookings on its own. I noticed The French Beauty Kuwait (Mangaf br.) and believe this would work great for you. A free demo of your site takes me about a day to make. Shall I send it?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-mangaf-br/</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1009,32 +961,28 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>The Body Spa</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>صالون The Body Spa</t>
-        </is>
-      </c>
+          <t>The French Beauty Kuwait (Salmiya br.)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Salmiya</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>+96527871478  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
+          <t>+96551284326  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-salmiya-br/</t>
         </is>
       </c>
       <c r="F14" s="3">
-        <f>HYPERLINK("https://wa.me/96527871478?text=Hello%20The%20Body%20Spa.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Kuwait.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20Body%20Spa%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96551284326?text=Hello%20The%20French%20Beauty%20Kuwait%20%28Salmiya%20br.%29.%20I%27m%20Jarvis%2C%20I%20look%20after%20KB%20Rewaq%20Digital%20and%20we%20set%20up%20automation%20for%20Kuwait%20salons.%20Based%20in%20Salmiya.%20We%20put%20your%20salon%20on%20a%20website%2C%20keep%20Instagram%20active%2C%20and%20let%20a%20WhatsApp%20bot%20answer%20booking%20requests%20day%20and%20night.%20The%20French%20Beauty%20Kuwait%20%28Salmiya%20br.%29%20stood%20out%20to%20me%20and%20I%20think%20automation%20would%20lift%20your%20bookings.%20I%20can%20draft%20a%20free%20demo%20site%20for%20you%20in%20a%20day.%20Interested%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-salmiya-br/","Click to DM")</f>
         <v/>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Hello The Body Spa. I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Kuwait. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The Body Spa stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-body-spa/</t>
+          <t>Hello The French Beauty Kuwait (Salmiya br.). I'm Jarvis, I look after KB Rewaq Digital and we set up automation for Kuwait salons. Based in Salmiya. We put your salon on a website, keep Instagram active, and let a WhatsApp bot answer booking requests day and night. The French Beauty Kuwait (Salmiya br.) stood out to me and I think automation would lift your bookings. I can draft a free demo site for you in a day. Interested?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-french-beauty-kuwait-salmiya-br/</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1049,75 +997,31 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>The Lounge Spa</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>صالون The Lounge Spa</t>
-        </is>
-      </c>
+          <t>Zircon Women Beauty Salon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Hawally</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>+96520230711  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/</t>
+          <t>+96599130939  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/zircon-women-beauty-salon/</t>
         </is>
       </c>
       <c r="F15" s="3">
-        <f>HYPERLINK("https://wa.me/96520230711?text=Good%20day%20The%20Lounge%20Spa.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Kuwait.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20The%20Lounge%20Spa%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/","Click to DM")</f>
+        <f>HYPERLINK("https://wa.me/96599130939?text=Good%20day%20Zircon%20Women%20Beauty%20Salon.%20Hey%2C%20Jarvis%20from%20KB%20Rewaq%20Digital.%20We%20handle%20automation%20for%20salons%20across%20Kuwait.%20Based%20in%20Hawally.%20Your%20business%20gets%20a%20live%20website%2C%20a%20services%20page%2C%20Instagram%20content%2C%20and%20a%20WhatsApp%20booking%20bot%20that%20replies%20to%20clients%2024/7%20while%20you%20focus%20on%20the%20salon.%20I%20saw%20Zircon%20Women%20Beauty%20Salon%20and%20your%20setup%20would%20fit%20this%20really%20well.%20I%20can%20put%20together%20a%20free%20demo%20of%20your%20own%20site%20in%20a%20day.%20Want%20me%20to%20send%20it%20over%3F%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/zircon-women-beauty-salon/","Click to DM")</f>
         <v/>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Good day The Lounge Spa. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Kuwait. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw The Lounge Spa and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/the-lounge-spa/</t>
+          <t>Good day Zircon Women Beauty Salon. Hey, Jarvis from KB Rewaq Digital. We handle automation for salons across Kuwait. Based in Hawally. Your business gets a live website, a services page, Instagram content, and a WhatsApp booking bot that replies to clients 24/7 while you focus on the salon. I saw Zircon Women Beauty Salon and your setup would fit this really well. I can put together a free demo of your own site in a day. Want me to send it over?
+Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/zircon-women-beauty-salon/</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Virgin Touch Salon</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>صالون Virgin Touch Salon</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>+96550703252  |  https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/</t>
-        </is>
-      </c>
-      <c r="F16" s="3">
-        <f>HYPERLINK("https://wa.me/96550703252?text=Hi%20there%20Virgin%20Touch%20Salon.%20I%27m%20Jarvis%2C%20manager%20at%20KB%20Rewaq%20Digital.%20I%20build%20automation%20systems%20for%20Kuwait%20salons%20and%20spas.%20Based%20in%20Kuwait.%20We%20give%20your%20salon%20a%20live%20site%2C%20social%20posts%2C%20and%20a%20WhatsApp%20bot%20that%20books%20clients%20for%20you%20around%20the%20clock.%20I%20came%20across%20Virgin%20Touch%20Salon%20and%20thought%20your%20place%20would%20suit%20this%20perfectly.%20I%20will%20build%20a%20free%20demo%20site%20for%20you%20in%20a%20day%20if%20you%20want%20to%20see%20it.%0A%0AHere%20is%20your%20free%20demo%20site%3A%20https%3A//faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/","Click to DM")</f>
-        <v/>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Hi there Virgin Touch Salon. I'm Jarvis, manager at KB Rewaq Digital. I build automation systems for Kuwait salons and spas. Based in Kuwait. We give your salon a live site, social posts, and a WhatsApp bot that books clients for you around the clock. I came across Virgin Touch Salon and thought your place would suit this perfectly. I will build a free demo site for you in a day if you want to see it.
-Here is your free demo site: https://faizanbashar215.github.io/kb-rewaq-digital/fresh_sites/virgin-touch-salon/</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
@@ -1215,7 +1119,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total fresh leads: 15   |   Live demo sites: 15</t>
+          <t>Total fresh leads: 14   |   Live demo sites: 14</t>
         </is>
       </c>
     </row>
